--- a/dapan/nangcao/DuLieuExcel_NC.xlsx
+++ b/dapan/nangcao/DuLieuExcel_NC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (3)\quiz-search\dapan\nangcao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (3)\quiz-search\dapan\nangcao\nc2604001\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1160,7 +1160,7 @@
     <col min="7" max="7" width="8.7265625" style="1"/>
     <col min="8" max="8" width="9.54296875" style="24" customWidth="1"/>
     <col min="9" max="9" width="26.1796875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.7265625" style="24" customWidth="1"/>
+    <col min="10" max="10" width="26.90625" style="24" customWidth="1"/>
     <col min="11" max="11" width="7.453125" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.7265625" style="1"/>
     <col min="13" max="13" width="16.54296875" style="1" customWidth="1"/>
